--- a/Odoo_Master_Data.xlsx
+++ b/Odoo_Master_Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" state="visible" r:id="rId3"/>
@@ -850,13 +850,13 @@
     <t xml:space="preserve">currency</t>
   </si>
   <si>
-    <t xml:space="preserve">WholeSale Price</t>
+    <t xml:space="preserve">جملة</t>
   </si>
   <si>
     <t xml:space="preserve">SYP</t>
   </si>
   <si>
-    <t xml:space="preserve">Sale Price</t>
+    <t xml:space="preserve">مفرق</t>
   </si>
   <si>
     <t xml:space="preserve">product_id</t>
@@ -892,7 +892,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,6 +929,12 @@
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans Devanagari"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1006,7 +1012,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1014,8 +1020,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1216,8 +1222,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="1" width="30.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="35.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16375" min="16373" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16376" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16373" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,7 +1269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1306,7 +1311,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -1348,7 +1353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -1390,7 +1395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1432,7 +1437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
@@ -1474,7 +1479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
@@ -1516,7 +1521,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -1558,7 +1563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
@@ -1600,7 +1605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
@@ -1642,7 +1647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
@@ -1684,7 +1689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -1726,7 +1731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1768,7 +1773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
@@ -1810,7 +1815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1852,7 +1857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -1894,7 +1899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -1936,7 +1941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -1978,7 +1983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -2020,7 +2025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
@@ -2062,7 +2067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -2104,7 +2109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>65</v>
       </c>
@@ -2146,7 +2151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
@@ -2188,7 +2193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>69</v>
       </c>
@@ -2230,7 +2235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>71</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
@@ -2314,7 +2319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>75</v>
       </c>
@@ -2356,7 +2361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
@@ -2398,7 +2403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
@@ -2440,7 +2445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>81</v>
       </c>
@@ -2482,7 +2487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>83</v>
       </c>
@@ -2524,7 +2529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>86</v>
       </c>
@@ -2566,7 +2571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
@@ -2608,7 +2613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>90</v>
       </c>
@@ -2650,7 +2655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>92</v>
       </c>
@@ -2692,7 +2697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>94</v>
       </c>
@@ -2734,7 +2739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>96</v>
       </c>
@@ -2776,7 +2781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>98</v>
       </c>
@@ -2818,7 +2823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>100</v>
       </c>
@@ -2860,7 +2865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>103</v>
       </c>
@@ -2902,7 +2907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>105</v>
       </c>
@@ -2944,7 +2949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>107</v>
       </c>
@@ -2986,7 +2991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
@@ -3028,7 +3033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>111</v>
       </c>
@@ -3070,7 +3075,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>113</v>
       </c>
@@ -3112,7 +3117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>115</v>
       </c>
@@ -3154,7 +3159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>117</v>
       </c>
@@ -3196,7 +3201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>119</v>
       </c>
@@ -3238,7 +3243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>121</v>
       </c>
@@ -3280,7 +3285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>123</v>
       </c>
@@ -3322,7 +3327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>125</v>
       </c>
@@ -3364,7 +3369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>127</v>
       </c>
@@ -3406,7 +3411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>129</v>
       </c>
@@ -3448,7 +3453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>131</v>
       </c>
@@ -3490,7 +3495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>133</v>
       </c>
@@ -3532,7 +3537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>135</v>
       </c>
@@ -3574,7 +3579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>137</v>
       </c>
@@ -3616,7 +3621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>139</v>
       </c>
@@ -3658,7 +3663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>141</v>
       </c>
@@ -3700,7 +3705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>144</v>
       </c>
@@ -3742,7 +3747,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>146</v>
       </c>
@@ -3784,7 +3789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>148</v>
       </c>
@@ -3826,7 +3831,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>150</v>
       </c>
@@ -3868,7 +3873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>152</v>
       </c>
@@ -3910,7 +3915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
         <v>154</v>
       </c>
@@ -3952,7 +3957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>156</v>
       </c>
@@ -3994,7 +3999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>158</v>
       </c>
@@ -4036,7 +4041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>160</v>
       </c>
@@ -4078,7 +4083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
         <v>162</v>
       </c>
@@ -4120,7 +4125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>164</v>
       </c>
@@ -4162,7 +4167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
         <v>166</v>
       </c>
@@ -4204,7 +4209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>168</v>
       </c>
@@ -4246,7 +4251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
         <v>170</v>
       </c>
@@ -4288,7 +4293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>172</v>
       </c>
@@ -4330,7 +4335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
         <v>174</v>
       </c>
@@ -4372,7 +4377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>176</v>
       </c>
@@ -4414,7 +4419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>178</v>
       </c>
@@ -4456,7 +4461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>180</v>
       </c>
@@ -4498,7 +4503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>182</v>
       </c>
@@ -4540,7 +4545,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>184</v>
       </c>
@@ -4582,7 +4587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>186</v>
       </c>
@@ -4624,7 +4629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>188</v>
       </c>
@@ -4666,7 +4671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
         <v>190</v>
       </c>
@@ -4708,7 +4713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>192</v>
       </c>
@@ -4750,7 +4755,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
         <v>194</v>
       </c>
@@ -4792,7 +4797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>196</v>
       </c>
@@ -4834,7 +4839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
         <v>198</v>
       </c>
@@ -4876,7 +4881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>200</v>
       </c>
@@ -4918,7 +4923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>202</v>
       </c>
@@ -4960,7 +4965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>204</v>
       </c>
@@ -5002,7 +5007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>206</v>
       </c>
@@ -5044,7 +5049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>208</v>
       </c>
@@ -5086,7 +5091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>210</v>
       </c>
@@ -5128,7 +5133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>212</v>
       </c>
@@ -5170,7 +5175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
         <v>214</v>
       </c>
@@ -5212,7 +5217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>216</v>
       </c>
@@ -5254,7 +5259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>218</v>
       </c>
@@ -5296,7 +5301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>220</v>
       </c>
@@ -5338,7 +5343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
         <v>222</v>
       </c>
@@ -5380,7 +5385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>224</v>
       </c>
@@ -5422,7 +5427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
         <v>226</v>
       </c>
@@ -5464,7 +5469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>229</v>
       </c>
@@ -5506,7 +5511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>231</v>
       </c>
@@ -5548,7 +5553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>233</v>
       </c>
@@ -5590,7 +5595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>235</v>
       </c>
@@ -5632,7 +5637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>237</v>
       </c>
@@ -5674,7 +5679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
         <v>239</v>
       </c>
@@ -5716,7 +5721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>241</v>
       </c>
@@ -5758,7 +5763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>243</v>
       </c>
@@ -5800,7 +5805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>245</v>
       </c>
@@ -5842,7 +5847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
         <v>247</v>
       </c>
@@ -5884,7 +5889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>249</v>
       </c>
@@ -5926,7 +5931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
         <v>251</v>
       </c>
@@ -5968,7 +5973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>253</v>
       </c>
@@ -6010,7 +6015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
         <v>255</v>
       </c>
@@ -6096,8 +6101,8 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>262</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -6114,7 +6119,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>259</v>
@@ -6128,7 +6133,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>259</v>
@@ -6142,7 +6147,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>259</v>
@@ -6156,7 +6161,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>259</v>
@@ -6170,7 +6175,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>259</v>
@@ -6184,7 +6189,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>259</v>
@@ -6198,7 +6203,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>259</v>
@@ -6212,7 +6217,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>259</v>
@@ -6226,7 +6231,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>259</v>
@@ -6240,7 +6245,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>259</v>
@@ -6254,7 +6259,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>259</v>
@@ -6268,7 +6273,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>259</v>
@@ -6282,7 +6287,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>259</v>
@@ -6296,7 +6301,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>259</v>
@@ -6310,7 +6315,7 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>259</v>
@@ -6324,7 +6329,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>259</v>
@@ -6338,7 +6343,7 @@
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>259</v>
@@ -6352,7 +6357,7 @@
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>259</v>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>259</v>
@@ -6380,7 +6385,7 @@
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>259</v>
@@ -6394,7 +6399,7 @@
       </c>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>259</v>
@@ -6408,7 +6413,7 @@
       </c>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>259</v>
@@ -6422,7 +6427,7 @@
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>259</v>
@@ -6436,7 +6441,7 @@
       </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>259</v>
@@ -6450,7 +6455,7 @@
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>259</v>
@@ -6464,7 +6469,7 @@
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>259</v>
@@ -6478,7 +6483,7 @@
       </c>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>259</v>
@@ -6492,7 +6497,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>259</v>
@@ -6506,7 +6511,7 @@
       </c>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>259</v>
@@ -6520,7 +6525,7 @@
       </c>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>259</v>
@@ -6534,7 +6539,7 @@
       </c>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>259</v>
@@ -6548,7 +6553,7 @@
       </c>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>259</v>
@@ -6562,7 +6567,7 @@
       </c>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>259</v>
@@ -6576,7 +6581,7 @@
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>259</v>
@@ -6590,7 +6595,7 @@
       </c>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>259</v>
@@ -6604,7 +6609,7 @@
       </c>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>259</v>
@@ -6618,7 +6623,7 @@
       </c>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="30.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>259</v>
@@ -6632,7 +6637,7 @@
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>259</v>
@@ -6646,7 +6651,7 @@
       </c>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>259</v>
@@ -6660,7 +6665,7 @@
       </c>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>259</v>
@@ -6674,7 +6679,7 @@
       </c>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>259</v>
@@ -6688,7 +6693,7 @@
       </c>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>259</v>
@@ -6702,7 +6707,7 @@
       </c>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>259</v>
@@ -6716,7 +6721,7 @@
       </c>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>259</v>
@@ -6730,7 +6735,7 @@
       </c>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>259</v>
@@ -6744,7 +6749,7 @@
       </c>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>259</v>
@@ -6758,7 +6763,7 @@
       </c>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>259</v>
@@ -6772,7 +6777,7 @@
       </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>259</v>
@@ -6786,7 +6791,7 @@
       </c>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>259</v>
@@ -6800,7 +6805,7 @@
       </c>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>259</v>
@@ -6814,7 +6819,7 @@
       </c>
       <c r="E52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>259</v>
@@ -6828,7 +6833,7 @@
       </c>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>259</v>
@@ -6842,7 +6847,7 @@
       </c>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>259</v>
@@ -6856,7 +6861,7 @@
       </c>
       <c r="E55" s="1"/>
     </row>
-    <row r="56" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>259</v>
@@ -6870,7 +6875,7 @@
       </c>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>259</v>
@@ -6884,7 +6889,7 @@
       </c>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>259</v>
@@ -6898,7 +6903,7 @@
       </c>
       <c r="E58" s="1"/>
     </row>
-    <row r="59" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>259</v>
@@ -6912,7 +6917,7 @@
       </c>
       <c r="E59" s="1"/>
     </row>
-    <row r="60" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>259</v>
@@ -6926,7 +6931,7 @@
       </c>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>259</v>
@@ -6940,7 +6945,7 @@
       </c>
       <c r="E61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>259</v>
@@ -6954,7 +6959,7 @@
       </c>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>259</v>
@@ -6968,7 +6973,7 @@
       </c>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>259</v>
@@ -6982,7 +6987,7 @@
       </c>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>259</v>
@@ -6996,7 +7001,7 @@
       </c>
       <c r="E65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>259</v>
@@ -7010,7 +7015,7 @@
       </c>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>259</v>
@@ -7024,7 +7029,7 @@
       </c>
       <c r="E67" s="1"/>
     </row>
-    <row r="68" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>259</v>
@@ -7038,7 +7043,7 @@
       </c>
       <c r="E68" s="1"/>
     </row>
-    <row r="69" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>259</v>
@@ -7052,7 +7057,7 @@
       </c>
       <c r="E69" s="1"/>
     </row>
-    <row r="70" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>259</v>
@@ -7066,7 +7071,7 @@
       </c>
       <c r="E70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>259</v>
@@ -7080,7 +7085,7 @@
       </c>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>259</v>
@@ -7094,7 +7099,7 @@
       </c>
       <c r="E72" s="1"/>
     </row>
-    <row r="73" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>259</v>
@@ -7108,7 +7113,7 @@
       </c>
       <c r="E73" s="1"/>
     </row>
-    <row r="74" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>259</v>
@@ -7122,7 +7127,7 @@
       </c>
       <c r="E74" s="1"/>
     </row>
-    <row r="75" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>259</v>
@@ -7136,7 +7141,7 @@
       </c>
       <c r="E75" s="1"/>
     </row>
-    <row r="76" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>259</v>
@@ -7150,7 +7155,7 @@
       </c>
       <c r="E76" s="1"/>
     </row>
-    <row r="77" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>259</v>
@@ -7164,7 +7169,7 @@
       </c>
       <c r="E77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>259</v>
@@ -7178,7 +7183,7 @@
       </c>
       <c r="E78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>259</v>
@@ -7192,7 +7197,7 @@
       </c>
       <c r="E79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>259</v>
@@ -7206,7 +7211,7 @@
       </c>
       <c r="E80" s="1"/>
     </row>
-    <row r="81" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>259</v>
@@ -7220,7 +7225,7 @@
       </c>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>259</v>
@@ -7234,7 +7239,7 @@
       </c>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>259</v>
@@ -7248,7 +7253,7 @@
       </c>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>259</v>
@@ -7262,7 +7267,7 @@
       </c>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>259</v>
@@ -7276,7 +7281,7 @@
       </c>
       <c r="E85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>259</v>
@@ -7290,7 +7295,7 @@
       </c>
       <c r="E86" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>259</v>
@@ -7304,7 +7309,7 @@
       </c>
       <c r="E87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>259</v>
@@ -7318,7 +7323,7 @@
       </c>
       <c r="E88" s="1"/>
     </row>
-    <row r="89" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>259</v>
@@ -7332,7 +7337,7 @@
       </c>
       <c r="E89" s="1"/>
     </row>
-    <row r="90" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>259</v>
@@ -7346,7 +7351,7 @@
       </c>
       <c r="E90" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>259</v>
@@ -7360,7 +7365,7 @@
       </c>
       <c r="E91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>259</v>
@@ -7374,7 +7379,7 @@
       </c>
       <c r="E92" s="1"/>
     </row>
-    <row r="93" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>259</v>
@@ -7388,7 +7393,7 @@
       </c>
       <c r="E93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>259</v>
@@ -7402,7 +7407,7 @@
       </c>
       <c r="E94" s="1"/>
     </row>
-    <row r="95" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>259</v>
@@ -7416,7 +7421,7 @@
       </c>
       <c r="E95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>259</v>
@@ -7430,7 +7435,7 @@
       </c>
       <c r="E96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>259</v>
@@ -7444,7 +7449,7 @@
       </c>
       <c r="E97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>259</v>
@@ -7458,7 +7463,7 @@
       </c>
       <c r="E98" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>259</v>
@@ -7472,7 +7477,7 @@
       </c>
       <c r="E99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>259</v>
@@ -7486,7 +7491,7 @@
       </c>
       <c r="E100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>259</v>
@@ -7500,7 +7505,7 @@
       </c>
       <c r="E101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>259</v>
@@ -7514,7 +7519,7 @@
       </c>
       <c r="E102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>259</v>
@@ -7528,7 +7533,7 @@
       </c>
       <c r="E103" s="1"/>
     </row>
-    <row r="104" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>259</v>
@@ -7542,7 +7547,7 @@
       </c>
       <c r="E104" s="1"/>
     </row>
-    <row r="105" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>259</v>
@@ -7556,7 +7561,7 @@
       </c>
       <c r="E105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>259</v>
@@ -7570,7 +7575,7 @@
       </c>
       <c r="E106" s="1"/>
     </row>
-    <row r="107" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>259</v>
@@ -7584,7 +7589,7 @@
       </c>
       <c r="E107" s="1"/>
     </row>
-    <row r="108" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>259</v>
@@ -7598,7 +7603,7 @@
       </c>
       <c r="E108" s="1"/>
     </row>
-    <row r="109" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>259</v>
@@ -7612,7 +7617,7 @@
       </c>
       <c r="E109" s="1"/>
     </row>
-    <row r="110" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>259</v>
@@ -7626,7 +7631,7 @@
       </c>
       <c r="E110" s="1"/>
     </row>
-    <row r="111" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>259</v>
@@ -7640,7 +7645,7 @@
       </c>
       <c r="E111" s="1"/>
     </row>
-    <row r="112" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>259</v>
@@ -7654,7 +7659,7 @@
       </c>
       <c r="E112" s="1"/>
     </row>
-    <row r="113" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>259</v>
@@ -7668,7 +7673,7 @@
       </c>
       <c r="E113" s="1"/>
     </row>
-    <row r="114" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>259</v>
@@ -7682,7 +7687,7 @@
       </c>
       <c r="E114" s="1"/>
     </row>
-    <row r="115" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>259</v>
@@ -7732,12 +7737,12 @@
       <c r="D1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>264</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -7750,11 +7755,11 @@
       <c r="D2" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="str">
@@ -7764,9 +7769,9 @@
       <c r="D3" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="str">
@@ -7776,9 +7781,9 @@
       <c r="D4" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="str">
@@ -7788,9 +7793,9 @@
       <c r="D5" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="str">
@@ -7800,9 +7805,9 @@
       <c r="D6" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="str">
@@ -7812,9 +7817,9 @@
       <c r="D7" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="str">
@@ -7824,9 +7829,9 @@
       <c r="D8" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="str">
@@ -7836,9 +7841,9 @@
       <c r="D9" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="str">
@@ -7848,9 +7853,9 @@
       <c r="D10" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="str">
@@ -7860,9 +7865,9 @@
       <c r="D11" s="6" t="n">
         <v>90000</v>
       </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="str">
@@ -7872,9 +7877,9 @@
       <c r="D12" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="str">
@@ -7884,9 +7889,9 @@
       <c r="D13" s="6" t="n">
         <v>85000</v>
       </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="str">
@@ -7896,9 +7901,9 @@
       <c r="D14" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="str">
@@ -7908,9 +7913,9 @@
       <c r="D15" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="str">
@@ -7920,9 +7925,9 @@
       <c r="D16" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="str">
@@ -7932,9 +7937,9 @@
       <c r="D17" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="str">
@@ -7944,9 +7949,9 @@
       <c r="D18" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="str">
@@ -7956,9 +7961,9 @@
       <c r="D19" s="6" t="n">
         <v>260000</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="str">
@@ -7968,9 +7973,9 @@
       <c r="D20" s="6" t="n">
         <v>225000</v>
       </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="str">
@@ -7980,9 +7985,9 @@
       <c r="D21" s="6" t="n">
         <v>150000</v>
       </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="str">
@@ -7992,9 +7997,9 @@
       <c r="D22" s="6" t="n">
         <v>240000</v>
       </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="str">
@@ -8004,9 +8009,9 @@
       <c r="D23" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="str">
@@ -8016,9 +8021,9 @@
       <c r="D24" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="str">
@@ -8028,9 +8033,9 @@
       <c r="D25" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="str">
@@ -8040,9 +8045,9 @@
       <c r="D26" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="str">
@@ -8052,9 +8057,9 @@
       <c r="D27" s="6" t="n">
         <v>600000</v>
       </c>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="str">
@@ -8064,9 +8069,9 @@
       <c r="D28" s="6" t="n">
         <v>530000</v>
       </c>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="str">
@@ -8076,9 +8081,9 @@
       <c r="D29" s="6" t="n">
         <v>300000</v>
       </c>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="str">
@@ -8088,9 +8093,9 @@
       <c r="D30" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="str">
@@ -8100,9 +8105,9 @@
       <c r="D31" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="str">
@@ -8112,9 +8117,9 @@
       <c r="D32" s="6" t="n">
         <v>190000</v>
       </c>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="str">
@@ -8124,9 +8129,9 @@
       <c r="D33" s="6" t="n">
         <v>230000</v>
       </c>
-      <c r="E33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="str">
@@ -8136,9 +8141,9 @@
       <c r="D34" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="str">
@@ -8148,9 +8153,9 @@
       <c r="D35" s="6" t="n">
         <v>140000</v>
       </c>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="str">
@@ -8160,9 +8165,9 @@
       <c r="D36" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="str">
@@ -8172,9 +8177,9 @@
       <c r="D37" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="str">
@@ -8184,9 +8189,9 @@
       <c r="D38" s="6" t="n">
         <v>65000</v>
       </c>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="30.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4" t="str">
@@ -8196,9 +8201,9 @@
       <c r="D39" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4" t="str">
@@ -8208,9 +8213,9 @@
       <c r="D40" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="E40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="str">
@@ -8220,9 +8225,9 @@
       <c r="D41" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4" t="str">
@@ -8232,9 +8237,9 @@
       <c r="D42" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4" t="str">
@@ -8244,9 +8249,9 @@
       <c r="D43" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4" t="str">
@@ -8256,9 +8261,9 @@
       <c r="D44" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="E44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4" t="str">
@@ -8268,9 +8273,9 @@
       <c r="D45" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4" t="str">
@@ -8280,9 +8285,9 @@
       <c r="D46" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4" t="str">
@@ -8292,9 +8297,9 @@
       <c r="D47" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="4" t="str">
@@ -8304,9 +8309,9 @@
       <c r="D48" s="6" t="n">
         <v>90000</v>
       </c>
-      <c r="E48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="4" t="str">
@@ -8316,9 +8321,9 @@
       <c r="D49" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="E49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4" t="str">
@@ -8328,9 +8333,9 @@
       <c r="D50" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="E50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="4" t="str">
@@ -8340,9 +8345,9 @@
       <c r="D51" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4" t="str">
@@ -8352,9 +8357,9 @@
       <c r="D52" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="E52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4" t="str">
@@ -8364,9 +8369,9 @@
       <c r="D53" s="6" t="n">
         <v>65000</v>
       </c>
-      <c r="E53" s="10"/>
-    </row>
-    <row r="54" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4" t="str">
@@ -8376,9 +8381,9 @@
       <c r="D54" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E54" s="10"/>
-    </row>
-    <row r="55" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4" t="str">
@@ -8388,9 +8393,9 @@
       <c r="D55" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="E55" s="10"/>
-    </row>
-    <row r="56" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4" t="str">
@@ -8400,9 +8405,9 @@
       <c r="D56" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E56" s="10"/>
-    </row>
-    <row r="57" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4" t="str">
@@ -8412,9 +8417,9 @@
       <c r="D57" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E57" s="10"/>
-    </row>
-    <row r="58" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4" t="str">
@@ -8424,9 +8429,9 @@
       <c r="D58" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E58" s="10"/>
-    </row>
-    <row r="59" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="8"/>
+    </row>
+    <row r="59" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4" t="str">
@@ -8436,9 +8441,9 @@
       <c r="D59" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E59" s="10"/>
-    </row>
-    <row r="60" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4" t="str">
@@ -8448,9 +8453,9 @@
       <c r="D60" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E60" s="10"/>
-    </row>
-    <row r="61" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="str">
@@ -8460,9 +8465,9 @@
       <c r="D61" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E61" s="10"/>
-    </row>
-    <row r="62" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="str">
@@ -8472,9 +8477,9 @@
       <c r="D62" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E62" s="10"/>
-    </row>
-    <row r="63" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="str">
@@ -8484,9 +8489,9 @@
       <c r="D63" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E63" s="10"/>
-    </row>
-    <row r="64" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="str">
@@ -8496,9 +8501,9 @@
       <c r="D64" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E64" s="10"/>
-    </row>
-    <row r="65" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="str">
@@ -8508,9 +8513,9 @@
       <c r="D65" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E65" s="10"/>
-    </row>
-    <row r="66" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="str">
@@ -8520,9 +8525,9 @@
       <c r="D66" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E66" s="10"/>
-    </row>
-    <row r="67" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="str">
@@ -8532,9 +8537,9 @@
       <c r="D67" s="6" t="n">
         <v>110000</v>
       </c>
-      <c r="E67" s="10"/>
-    </row>
-    <row r="68" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="str">
@@ -8544,9 +8549,9 @@
       <c r="D68" s="6" t="n">
         <v>190000</v>
       </c>
-      <c r="E68" s="10"/>
-    </row>
-    <row r="69" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4" t="str">
@@ -8556,9 +8561,9 @@
       <c r="D69" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E69" s="10"/>
-    </row>
-    <row r="70" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4" t="str">
@@ -8568,9 +8573,9 @@
       <c r="D70" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E70" s="10"/>
-    </row>
-    <row r="71" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4" t="str">
@@ -8580,9 +8585,9 @@
       <c r="D71" s="6" t="n">
         <v>70000</v>
       </c>
-      <c r="E71" s="10"/>
-    </row>
-    <row r="72" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4" t="str">
@@ -8592,9 +8597,9 @@
       <c r="D72" s="6" t="n">
         <v>250000</v>
       </c>
-      <c r="E72" s="10"/>
-    </row>
-    <row r="73" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4" t="str">
@@ -8604,9 +8609,9 @@
       <c r="D73" s="6" t="n">
         <v>180000</v>
       </c>
-      <c r="E73" s="10"/>
-    </row>
-    <row r="74" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E73" s="8"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="str">
@@ -8616,9 +8621,9 @@
       <c r="D74" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="E74" s="10"/>
-    </row>
-    <row r="75" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="str">
@@ -8628,9 +8633,9 @@
       <c r="D75" s="6" t="n">
         <v>200000</v>
       </c>
-      <c r="E75" s="10"/>
-    </row>
-    <row r="76" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4" t="str">
@@ -8640,9 +8645,9 @@
       <c r="D76" s="6" t="n">
         <v>200000</v>
       </c>
-      <c r="E76" s="10"/>
-    </row>
-    <row r="77" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="8"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4" t="str">
@@ -8652,9 +8657,9 @@
       <c r="D77" s="6" t="n">
         <v>160000</v>
       </c>
-      <c r="E77" s="10"/>
-    </row>
-    <row r="78" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4" t="str">
@@ -8664,9 +8669,9 @@
       <c r="D78" s="6" t="n">
         <v>140000</v>
       </c>
-      <c r="E78" s="10"/>
-    </row>
-    <row r="79" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="8"/>
+    </row>
+    <row r="79" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4" t="str">
@@ -8676,9 +8681,9 @@
       <c r="D79" s="6" t="n">
         <v>90000</v>
       </c>
-      <c r="E79" s="10"/>
-    </row>
-    <row r="80" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4" t="str">
@@ -8688,9 +8693,9 @@
       <c r="D80" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E80" s="10"/>
-    </row>
-    <row r="81" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E80" s="8"/>
+    </row>
+    <row r="81" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4" t="str">
@@ -8700,9 +8705,9 @@
       <c r="D81" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E81" s="10"/>
-    </row>
-    <row r="82" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4" t="str">
@@ -8712,9 +8717,9 @@
       <c r="D82" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E82" s="10"/>
-    </row>
-    <row r="83" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4" t="str">
@@ -8724,9 +8729,9 @@
       <c r="D83" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E83" s="10"/>
-    </row>
-    <row r="84" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E83" s="8"/>
+    </row>
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4" t="str">
@@ -8736,9 +8741,9 @@
       <c r="D84" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E84" s="10"/>
-    </row>
-    <row r="85" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E84" s="8"/>
+    </row>
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4" t="str">
@@ -8748,9 +8753,9 @@
       <c r="D85" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E85" s="10"/>
-    </row>
-    <row r="86" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E85" s="8"/>
+    </row>
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4" t="str">
@@ -8760,9 +8765,9 @@
       <c r="D86" s="6" t="n">
         <v>90000</v>
       </c>
-      <c r="E86" s="10"/>
-    </row>
-    <row r="87" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E86" s="8"/>
+    </row>
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4" t="str">
@@ -8772,9 +8777,9 @@
       <c r="D87" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E87" s="10"/>
-    </row>
-    <row r="88" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="8"/>
+    </row>
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4" t="str">
@@ -8784,9 +8789,9 @@
       <c r="D88" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E88" s="10"/>
-    </row>
-    <row r="89" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="8"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4" t="str">
@@ -8796,9 +8801,9 @@
       <c r="D89" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E89" s="10"/>
-    </row>
-    <row r="90" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E89" s="8"/>
+    </row>
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4" t="str">
@@ -8808,9 +8813,9 @@
       <c r="D90" s="6" t="n">
         <v>180000</v>
       </c>
-      <c r="E90" s="10"/>
-    </row>
-    <row r="91" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E90" s="8"/>
+    </row>
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4" t="str">
@@ -8820,9 +8825,9 @@
       <c r="D91" s="6" t="n">
         <v>180000</v>
       </c>
-      <c r="E91" s="10"/>
-    </row>
-    <row r="92" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="8"/>
+    </row>
+    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4" t="str">
@@ -8832,9 +8837,9 @@
       <c r="D92" s="6" t="n">
         <v>260000</v>
       </c>
-      <c r="E92" s="10"/>
-    </row>
-    <row r="93" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="8"/>
+    </row>
+    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4" t="str">
@@ -8844,9 +8849,9 @@
       <c r="D93" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="E93" s="10"/>
-    </row>
-    <row r="94" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E93" s="8"/>
+    </row>
+    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4" t="str">
@@ -8856,9 +8861,9 @@
       <c r="D94" s="6" t="n">
         <v>190000</v>
       </c>
-      <c r="E94" s="10"/>
-    </row>
-    <row r="95" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E94" s="8"/>
+    </row>
+    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4" t="str">
@@ -8868,9 +8873,9 @@
       <c r="D95" s="6" t="n">
         <v>160000</v>
       </c>
-      <c r="E95" s="10"/>
-    </row>
-    <row r="96" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="8"/>
+    </row>
+    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4" t="str">
@@ -8880,9 +8885,9 @@
       <c r="D96" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E96" s="10"/>
-    </row>
-    <row r="97" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="8"/>
+    </row>
+    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4" t="str">
@@ -8892,9 +8897,9 @@
       <c r="D97" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="E97" s="10"/>
-    </row>
-    <row r="98" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E97" s="8"/>
+    </row>
+    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4" t="str">
@@ -8904,9 +8909,9 @@
       <c r="D98" s="6" t="n">
         <v>330000</v>
       </c>
-      <c r="E98" s="10"/>
-    </row>
-    <row r="99" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E98" s="8"/>
+    </row>
+    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4" t="str">
@@ -8916,9 +8921,9 @@
       <c r="D99" s="6" t="n">
         <v>400000</v>
       </c>
-      <c r="E99" s="10"/>
-    </row>
-    <row r="100" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E99" s="8"/>
+    </row>
+    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4" t="str">
@@ -8928,9 +8933,9 @@
       <c r="D100" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E100" s="10"/>
-    </row>
-    <row r="101" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="8"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4" t="str">
@@ -8940,9 +8945,9 @@
       <c r="D101" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="E101" s="10"/>
-    </row>
-    <row r="102" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4" t="str">
@@ -8952,9 +8957,9 @@
       <c r="D102" s="6" t="n">
         <v>140000</v>
       </c>
-      <c r="E102" s="10"/>
-    </row>
-    <row r="103" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E102" s="8"/>
+    </row>
+    <row r="103" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4" t="str">
@@ -8964,9 +8969,9 @@
       <c r="D103" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="E103" s="10"/>
-    </row>
-    <row r="104" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E103" s="8"/>
+    </row>
+    <row r="104" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4" t="str">
@@ -8976,9 +8981,9 @@
       <c r="D104" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="E104" s="10"/>
-    </row>
-    <row r="105" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E104" s="8"/>
+    </row>
+    <row r="105" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="4" t="str">
@@ -8988,9 +8993,9 @@
       <c r="D105" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="E105" s="10"/>
-    </row>
-    <row r="106" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="8"/>
+    </row>
+    <row r="106" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="4" t="str">
@@ -9000,9 +9005,9 @@
       <c r="D106" s="6" t="n">
         <v>190000</v>
       </c>
-      <c r="E106" s="10"/>
-    </row>
-    <row r="107" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="8"/>
+    </row>
+    <row r="107" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="4" t="str">
@@ -9012,9 +9017,9 @@
       <c r="D107" s="6" t="n">
         <v>170000</v>
       </c>
-      <c r="E107" s="10"/>
-    </row>
-    <row r="108" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="8"/>
+    </row>
+    <row r="108" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4" t="str">
@@ -9024,9 +9029,9 @@
       <c r="D108" s="6" t="n">
         <v>60000</v>
       </c>
-      <c r="E108" s="10"/>
-    </row>
-    <row r="109" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="8"/>
+    </row>
+    <row r="109" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4" t="str">
@@ -9036,9 +9041,9 @@
       <c r="D109" s="6" t="n">
         <v>320000</v>
       </c>
-      <c r="E109" s="10"/>
-    </row>
-    <row r="110" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E109" s="8"/>
+    </row>
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4" t="str">
@@ -9048,9 +9053,9 @@
       <c r="D110" s="6" t="n">
         <v>80000</v>
       </c>
-      <c r="E110" s="10"/>
-    </row>
-    <row r="111" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="8"/>
+    </row>
+    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4" t="str">
@@ -9060,9 +9065,9 @@
       <c r="D111" s="6" t="n">
         <v>220000</v>
       </c>
-      <c r="E111" s="10"/>
-    </row>
-    <row r="112" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="8"/>
+    </row>
+    <row r="112" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4" t="str">
@@ -9072,9 +9077,9 @@
       <c r="D112" s="6" t="n">
         <v>140000</v>
       </c>
-      <c r="E112" s="10"/>
-    </row>
-    <row r="113" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E112" s="8"/>
+    </row>
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4" t="str">
@@ -9084,9 +9089,9 @@
       <c r="D113" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="E113" s="10"/>
-    </row>
-    <row r="114" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E113" s="8"/>
+    </row>
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4" t="str">
@@ -9096,9 +9101,9 @@
       <c r="D114" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="E114" s="10"/>
-    </row>
-    <row r="115" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E114" s="8"/>
+    </row>
+    <row r="115" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4" t="str">
@@ -9108,7 +9113,7 @@
       <c r="D115" s="6" t="n">
         <v>45000</v>
       </c>
-      <c r="E115" s="10"/>
+      <c r="E115" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9149,7 +9154,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -9163,7 +9168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
@@ -9177,7 +9182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
@@ -9191,7 +9196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -9205,7 +9210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -9219,7 +9224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
@@ -9233,7 +9238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -9247,7 +9252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
@@ -9261,7 +9266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -9275,7 +9280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
@@ -9289,7 +9294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>44</v>
       </c>
@@ -9303,7 +9308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
@@ -9317,7 +9322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
@@ -9331,7 +9336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
@@ -9345,7 +9350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>52</v>
       </c>
@@ -9359,7 +9364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>54</v>
       </c>
@@ -9373,7 +9378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>56</v>
       </c>
@@ -9387,7 +9392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>58</v>
       </c>
@@ -9401,7 +9406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -9415,7 +9420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>64</v>
       </c>
@@ -9429,7 +9434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>66</v>
       </c>
@@ -9443,7 +9448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>68</v>
       </c>
@@ -9457,7 +9462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>70</v>
       </c>
@@ -9471,7 +9476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>72</v>
       </c>
@@ -9485,7 +9490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>74</v>
       </c>
@@ -9499,7 +9504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>76</v>
       </c>
@@ -9513,7 +9518,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>78</v>
       </c>
@@ -9527,7 +9532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>80</v>
       </c>
@@ -9541,7 +9546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>82</v>
       </c>
@@ -9555,7 +9560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>84</v>
       </c>
@@ -9569,7 +9574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
         <v>87</v>
       </c>
@@ -9583,7 +9588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>89</v>
       </c>
@@ -9597,7 +9602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>91</v>
       </c>
@@ -9611,7 +9616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>93</v>
       </c>
@@ -9625,7 +9630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>95</v>
       </c>
@@ -9639,7 +9644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>97</v>
       </c>
@@ -9653,7 +9658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>99</v>
       </c>
@@ -9667,7 +9672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
@@ -9681,7 +9686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
         <v>104</v>
       </c>
@@ -9695,7 +9700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>106</v>
       </c>
@@ -9709,7 +9714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>108</v>
       </c>
@@ -9723,7 +9728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
         <v>110</v>
       </c>
@@ -9737,7 +9742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
         <v>112</v>
       </c>
@@ -9751,7 +9756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
         <v>114</v>
       </c>
@@ -9765,7 +9770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
         <v>116</v>
       </c>
@@ -9779,7 +9784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
         <v>118</v>
       </c>
@@ -9793,7 +9798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
         <v>120</v>
       </c>
@@ -9807,7 +9812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
         <v>122</v>
       </c>
@@ -9821,7 +9826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
         <v>124</v>
       </c>
@@ -9835,7 +9840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
         <v>126</v>
       </c>
@@ -9849,7 +9854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
         <v>128</v>
       </c>
@@ -9863,7 +9868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>130</v>
       </c>
@@ -9877,7 +9882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
         <v>132</v>
       </c>
@@ -9891,7 +9896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
         <v>134</v>
       </c>
@@ -9905,7 +9910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
         <v>136</v>
       </c>
@@ -9919,7 +9924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
         <v>138</v>
       </c>
@@ -9933,7 +9938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
         <v>140</v>
       </c>
@@ -9947,7 +9952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
         <v>142</v>
       </c>
@@ -9961,7 +9966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
         <v>145</v>
       </c>
@@ -9975,7 +9980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
         <v>147</v>
       </c>
@@ -9989,7 +9994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
         <v>149</v>
       </c>
@@ -10003,7 +10008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
         <v>151</v>
       </c>
@@ -10017,7 +10022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
         <v>153</v>
       </c>
@@ -10031,7 +10036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>155</v>
       </c>
@@ -10045,7 +10050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
         <v>157</v>
       </c>
@@ -10059,7 +10064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>159</v>
       </c>
@@ -10073,7 +10078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
         <v>161</v>
       </c>
@@ -10087,7 +10092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>163</v>
       </c>
@@ -10101,7 +10106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
         <v>165</v>
       </c>
@@ -10115,7 +10120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
         <v>167</v>
       </c>
@@ -10129,7 +10134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
         <v>169</v>
       </c>
@@ -10143,7 +10148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
         <v>171</v>
       </c>
@@ -10157,7 +10162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
         <v>173</v>
       </c>
@@ -10171,7 +10176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
         <v>175</v>
       </c>
@@ -10185,7 +10190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
         <v>177</v>
       </c>
@@ -10199,7 +10204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
         <v>179</v>
       </c>
@@ -10213,7 +10218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
         <v>181</v>
       </c>
@@ -10227,7 +10232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
         <v>183</v>
       </c>
@@ -10241,7 +10246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
         <v>185</v>
       </c>
@@ -10255,7 +10260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
         <v>187</v>
       </c>
@@ -10269,7 +10274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
         <v>189</v>
       </c>
@@ -10283,7 +10288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
         <v>191</v>
       </c>
@@ -10297,7 +10302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
         <v>193</v>
       </c>
@@ -10311,7 +10316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
         <v>195</v>
       </c>
@@ -10325,7 +10330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
         <v>197</v>
       </c>
@@ -10339,7 +10344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
         <v>199</v>
       </c>
@@ -10353,7 +10358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>201</v>
       </c>
@@ -10367,7 +10372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
         <v>203</v>
       </c>
@@ -10381,7 +10386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
         <v>205</v>
       </c>
@@ -10395,7 +10400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
         <v>207</v>
       </c>
@@ -10409,7 +10414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
         <v>209</v>
       </c>
@@ -10423,7 +10428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
         <v>211</v>
       </c>
@@ -10437,7 +10442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
         <v>213</v>
       </c>
@@ -10451,7 +10456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
         <v>215</v>
       </c>
@@ -10465,7 +10470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
         <v>217</v>
       </c>
@@ -10479,7 +10484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>219</v>
       </c>
@@ -10493,7 +10498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
         <v>221</v>
       </c>
@@ -10507,7 +10512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
         <v>223</v>
       </c>
@@ -10521,7 +10526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
         <v>225</v>
       </c>
@@ -10535,7 +10540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
         <v>227</v>
       </c>
@@ -10549,7 +10554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
         <v>230</v>
       </c>
@@ -10563,7 +10568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
         <v>232</v>
       </c>
@@ -10577,7 +10582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
         <v>234</v>
       </c>
@@ -10591,7 +10596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
         <v>236</v>
       </c>
@@ -10605,7 +10610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
         <v>238</v>
       </c>
@@ -10619,7 +10624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
         <v>240</v>
       </c>
@@ -10633,7 +10638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
         <v>242</v>
       </c>
@@ -10647,7 +10652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
         <v>244</v>
       </c>
@@ -10661,7 +10666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
         <v>246</v>
       </c>
@@ -10675,7 +10680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
         <v>248</v>
       </c>
@@ -10689,7 +10694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
         <v>250</v>
       </c>
@@ -10703,7 +10708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
         <v>252</v>
       </c>
@@ -10717,7 +10722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
         <v>254</v>
       </c>
@@ -10731,7 +10736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
         <v>256</v>
       </c>
@@ -10788,7 +10793,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -10805,7 +10810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -10822,7 +10827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -10839,7 +10844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -10856,7 +10861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
@@ -10873,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
@@ -10890,7 +10895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -10907,7 +10912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
@@ -10924,7 +10929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
@@ -10941,7 +10946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
@@ -10958,7 +10963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -10975,7 +10980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -10992,7 +10997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
@@ -11009,7 +11014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
@@ -11026,7 +11031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -11043,7 +11048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -11060,7 +11065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -11077,7 +11082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -11094,7 +11099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
@@ -11111,7 +11116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -11128,7 +11133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>65</v>
       </c>
@@ -11145,7 +11150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
@@ -11162,7 +11167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>69</v>
       </c>
@@ -11179,7 +11184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>71</v>
       </c>
@@ -11196,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
@@ -11213,7 +11218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>75</v>
       </c>
@@ -11230,7 +11235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
@@ -11247,7 +11252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>79</v>
       </c>
@@ -11264,7 +11269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>81</v>
       </c>
@@ -11281,7 +11286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>83</v>
       </c>
@@ -11298,7 +11303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>86</v>
       </c>
@@ -11315,7 +11320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
@@ -11332,7 +11337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>90</v>
       </c>
@@ -11349,7 +11354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>92</v>
       </c>
@@ -11366,7 +11371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>94</v>
       </c>
@@ -11383,7 +11388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>96</v>
       </c>
@@ -11400,7 +11405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>98</v>
       </c>
@@ -11417,7 +11422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>100</v>
       </c>
@@ -11434,7 +11439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>103</v>
       </c>
@@ -11451,7 +11456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>105</v>
       </c>
@@ -11468,7 +11473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>107</v>
       </c>
@@ -11485,7 +11490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
@@ -11502,7 +11507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>111</v>
       </c>
@@ -11519,7 +11524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>113</v>
       </c>
@@ -11536,7 +11541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>115</v>
       </c>
@@ -11553,7 +11558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>117</v>
       </c>
@@ -11570,7 +11575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>119</v>
       </c>
@@ -11587,7 +11592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>121</v>
       </c>
@@ -11604,7 +11609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>123</v>
       </c>
@@ -11621,7 +11626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>125</v>
       </c>
@@ -11638,7 +11643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>127</v>
       </c>
@@ -11655,7 +11660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>129</v>
       </c>
@@ -11672,7 +11677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>131</v>
       </c>
@@ -11689,7 +11694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>133</v>
       </c>
@@ -11706,7 +11711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>135</v>
       </c>
@@ -11723,7 +11728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>137</v>
       </c>
@@ -11740,7 +11745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>139</v>
       </c>
@@ -11757,7 +11762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>141</v>
       </c>
@@ -11774,7 +11779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>144</v>
       </c>
@@ -11791,7 +11796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>146</v>
       </c>
@@ -11808,7 +11813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>148</v>
       </c>
@@ -11825,7 +11830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>150</v>
       </c>
@@ -11842,7 +11847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>152</v>
       </c>
@@ -11859,7 +11864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
         <v>154</v>
       </c>
@@ -11876,7 +11881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>156</v>
       </c>
@@ -11893,7 +11898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>158</v>
       </c>
@@ -11910,7 +11915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>160</v>
       </c>
@@ -11927,7 +11932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
         <v>162</v>
       </c>
@@ -11944,7 +11949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>164</v>
       </c>
@@ -11961,7 +11966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
         <v>166</v>
       </c>
@@ -11978,7 +11983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>168</v>
       </c>
@@ -11995,7 +12000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
         <v>170</v>
       </c>
@@ -12012,7 +12017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>172</v>
       </c>
@@ -12029,7 +12034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
         <v>174</v>
       </c>
@@ -12046,7 +12051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>176</v>
       </c>
@@ -12063,7 +12068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>178</v>
       </c>
@@ -12080,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>180</v>
       </c>
@@ -12097,7 +12102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>182</v>
       </c>
@@ -12114,7 +12119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>184</v>
       </c>
@@ -12131,7 +12136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>186</v>
       </c>
@@ -12148,7 +12153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>188</v>
       </c>
@@ -12165,7 +12170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
         <v>190</v>
       </c>
@@ -12182,7 +12187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>192</v>
       </c>
@@ -12199,7 +12204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
         <v>194</v>
       </c>
@@ -12216,7 +12221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>196</v>
       </c>
@@ -12233,7 +12238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
         <v>198</v>
       </c>
@@ -12250,7 +12255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>200</v>
       </c>
@@ -12267,7 +12272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>202</v>
       </c>
@@ -12284,7 +12289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>204</v>
       </c>
@@ -12301,7 +12306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>206</v>
       </c>
@@ -12318,7 +12323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>208</v>
       </c>
@@ -12335,7 +12340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>210</v>
       </c>
@@ -12352,7 +12357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>212</v>
       </c>
@@ -12369,7 +12374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
         <v>214</v>
       </c>
@@ -12386,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>216</v>
       </c>
@@ -12403,7 +12408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>218</v>
       </c>
@@ -12420,7 +12425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>220</v>
       </c>
@@ -12437,7 +12442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
         <v>222</v>
       </c>
@@ -12454,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>224</v>
       </c>
@@ -12471,7 +12476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
         <v>226</v>
       </c>
@@ -12488,7 +12493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>229</v>
       </c>
@@ -12505,7 +12510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>231</v>
       </c>
@@ -12522,7 +12527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>233</v>
       </c>
@@ -12539,7 +12544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>235</v>
       </c>
@@ -12556,7 +12561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>237</v>
       </c>
@@ -12573,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
         <v>239</v>
       </c>
@@ -12590,7 +12595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>241</v>
       </c>
@@ -12607,7 +12612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>243</v>
       </c>
@@ -12624,7 +12629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>245</v>
       </c>
@@ -12641,7 +12646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
         <v>247</v>
       </c>
@@ -12658,7 +12663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>249</v>
       </c>
@@ -12675,7 +12680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
         <v>251</v>
       </c>
@@ -12692,7 +12697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>253</v>
       </c>
@@ -12709,7 +12714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
         <v>255</v>
       </c>
